--- a/ap project documents/AP_project_2026_one_team_tracker.xlsx
+++ b/ap project documents/AP_project_2026_one_team_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HAMAHANG\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arian\Desktop\uni\AP\Project\Plants-vs-Zombies-2\ap project documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D66F329-02CE-4805-936D-7904C150510C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FA4A14-6656-4A42-BF40-3DF7B1EA6FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="7" r:id="rId1"/>
@@ -21,7 +21,23 @@
     <sheet name="_logic_p1" sheetId="2" state="hidden" r:id="rId6"/>
     <sheet name="_logic_p2" sheetId="3" state="hidden" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2844,27 +2860,18 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2894,6 +2901,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3328,38 +3344,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.8" customHeight="1">
-      <c r="A1" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="A1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="5" spans="1:8" ht="27.15" customHeight="1">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
@@ -3374,11 +3390,11 @@
       <c r="D7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="F7" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
@@ -3396,11 +3412,11 @@
         <f t="shared" ref="D8:D14" si="0">IF(C8=0,0,B8/C8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="53" t="s">
+      <c r="F8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="54"/>
-      <c r="H8" s="55"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="50"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="5" t="s">
@@ -3418,9 +3434,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="56"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="58"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="53"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="5" t="s">
@@ -3438,9 +3454,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="56"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="58"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="53"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="5" t="s">
@@ -3448,7 +3464,7 @@
       </c>
       <c r="B11" s="36">
         <f>_logic_p2!IF5</f>
-        <v>2960</v>
+        <v>3520</v>
       </c>
       <c r="C11" s="30">
         <f>_logic_p2!IF4</f>
@@ -3456,11 +3472,11 @@
       </c>
       <c r="D11" s="33">
         <f t="shared" si="0"/>
-        <v>0.73176761433868975</v>
-      </c>
-      <c r="F11" s="56"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="58"/>
+        <v>0.8702101359703337</v>
+      </c>
+      <c r="F11" s="51"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="53"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
@@ -3478,9 +3494,9 @@
         <f t="shared" si="0"/>
         <v>0.15051546391752577</v>
       </c>
-      <c r="F12" s="56"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="58"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="53"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="5" t="s">
@@ -3488,7 +3504,7 @@
       </c>
       <c r="B13" s="36">
         <f>_logic_p2!IH5</f>
-        <v>3325</v>
+        <v>3885</v>
       </c>
       <c r="C13" s="30">
         <f>_logic_p2!IH4</f>
@@ -3496,11 +3512,11 @@
       </c>
       <c r="D13" s="33">
         <f t="shared" si="0"/>
-        <v>0.82200247218788625</v>
-      </c>
-      <c r="F13" s="56"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="58"/>
+        <v>0.9604449938195303</v>
+      </c>
+      <c r="F13" s="51"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="53"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="6" t="s">
@@ -3518,21 +3534,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="61"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="56"/>
     </row>
     <row r="16" spans="1:8" ht="14.4">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3603,58 +3619,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.65" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="45" t="str">
+      <c r="B3" s="57" t="str">
         <f>Dashboard!$B$3</f>
         <v>My Team</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="47"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
     </row>
     <row r="5" spans="1:11" ht="22.35" customHeight="1">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="41"/>
+      <c r="B7" s="60"/>
     </row>
     <row r="8" spans="1:11" ht="17.399999999999999">
-      <c r="A8" s="42" t="str">
+      <c r="A8" s="61" t="str">
         <f>IF(_logic_p0!BA5="",0,_logic_p0!BA5)&amp;" / "&amp;_logic_p0!BA4</f>
         <v>0 / 380</v>
       </c>
-      <c r="B8" s="42"/>
+      <c r="B8" s="61"/>
     </row>
     <row r="10" spans="1:11" ht="24" customHeight="1">
       <c r="A10" s="2" t="s">
@@ -5580,67 +5596,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.65" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="45" t="str">
+      <c r="B3" s="57" t="str">
         <f>Dashboard!$B$3</f>
         <v>My Team</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="47"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
     </row>
     <row r="5" spans="1:11" ht="22.35" customHeight="1">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41" t="s">
+      <c r="A7" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="41"/>
+      <c r="D7" s="60"/>
     </row>
     <row r="8" spans="1:11" ht="17.399999999999999">
-      <c r="A8" s="42" t="str">
+      <c r="A8" s="61" t="str">
         <f>_logic_p1!EE5&amp;" / "&amp;_logic_p1!EE4</f>
         <v>0 / 5495</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42" t="str">
+      <c r="B8" s="61"/>
+      <c r="C8" s="61" t="str">
         <f>_logic_p1!EF5&amp;" / "&amp;_logic_p1!EF4</f>
         <v>0 / 60</v>
       </c>
-      <c r="D8" s="42"/>
+      <c r="D8" s="61"/>
     </row>
     <row r="10" spans="1:11" ht="24" customHeight="1">
       <c r="A10" s="2" t="s">
@@ -10340,85 +10356,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.65" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="42" t="s">
         <v>393</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="45" t="str">
+      <c r="B3" s="57" t="str">
         <f>Dashboard!$B$3</f>
         <v>My Team</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="47"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="59"/>
     </row>
     <row r="5" spans="1:11" ht="22.35" customHeight="1">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41" t="s">
+      <c r="A7" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60" t="s">
         <v>394</v>
       </c>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41" t="s">
+      <c r="D7" s="60"/>
+      <c r="E7" s="60" t="s">
         <v>395</v>
       </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41" t="s">
+      <c r="F7" s="60"/>
+      <c r="G7" s="60" t="s">
         <v>156</v>
       </c>
-      <c r="H7" s="41"/>
+      <c r="H7" s="60"/>
     </row>
     <row r="8" spans="1:11" ht="17.399999999999999">
-      <c r="A8" s="42" t="str">
+      <c r="A8" s="61" t="str">
         <f>_logic_p2!IF5&amp;" / "&amp;_logic_p2!IF4</f>
-        <v>2960 / 4045</v>
-      </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42" t="str">
+        <v>3520 / 4045</v>
+      </c>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61" t="str">
         <f>_logic_p2!IG5&amp;" / "&amp;_logic_p2!IG4</f>
         <v>365 / 2425</v>
       </c>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42" t="str">
+      <c r="D8" s="61"/>
+      <c r="E8" s="61" t="str">
         <f>_logic_p2!IH5&amp;" / "&amp;_logic_p2!IH4</f>
-        <v>3325 / 4045</v>
-      </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42" t="str">
+        <v>3885 / 4045</v>
+      </c>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61" t="str">
         <f>_logic_p2!II5&amp;" / "&amp;_logic_p2!II4</f>
         <v>0 / 835</v>
       </c>
-      <c r="H8" s="42"/>
+      <c r="H8" s="61"/>
     </row>
     <row r="10" spans="1:11" ht="24" customHeight="1">
       <c r="A10" s="2" t="s">
@@ -12809,20 +12825,20 @@
         <v>40</v>
       </c>
       <c r="E76" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="20"/>
       <c r="G76" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H76" s="14">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I76" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: گزینه ورود به مینی‌گیم‌ها</v>
+        <v>Done</v>
       </c>
       <c r="J76" s="39" t="s">
         <v>155</v>
@@ -13565,20 +13581,20 @@
         <v>75</v>
       </c>
       <c r="E97" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="20"/>
       <c r="G97" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H97" s="14">
         <f t="shared" si="4"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I97" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: انواع پرتابه‌ها</v>
+        <v>Done</v>
       </c>
       <c r="J97" s="39" t="s">
         <v>155</v>
@@ -13601,20 +13617,20 @@
         <v>100</v>
       </c>
       <c r="E98" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="20"/>
       <c r="G98" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H98" s="14">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I98" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: برخورد پرتابه‌ها</v>
+        <v>Done</v>
       </c>
       <c r="J98" s="39" t="s">
         <v>155</v>
@@ -13889,20 +13905,20 @@
         <v>15</v>
       </c>
       <c r="E106" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="20"/>
       <c r="G106" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H106" s="14">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I106" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: نمایش قبرها</v>
+        <v>Done</v>
       </c>
       <c r="J106" s="39" t="s">
         <v>155</v>
@@ -14861,20 +14877,20 @@
         <v>30</v>
       </c>
       <c r="E133" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="20"/>
       <c r="G133" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H133" s="14">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I133" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: کوزه‌ها و انواعشان</v>
+        <v>Done</v>
       </c>
       <c r="J133" s="39" t="s">
         <v>155</v>
@@ -14897,20 +14913,20 @@
         <v>25</v>
       </c>
       <c r="E134" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="20"/>
       <c r="G134" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H134" s="14">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I134" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: شکستن کوزه‌ها</v>
+        <v>Done</v>
       </c>
       <c r="J134" s="39" t="s">
         <v>155</v>
@@ -14933,20 +14949,20 @@
         <v>35</v>
       </c>
       <c r="E135" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="20"/>
       <c r="G135" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H135" s="14">
         <f t="shared" si="4"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I135" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: کاشت</v>
+        <v>Done</v>
       </c>
       <c r="J135" s="39" t="s">
         <v>155</v>
@@ -14969,20 +14985,20 @@
         <v>25</v>
       </c>
       <c r="E136" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="20"/>
       <c r="G136" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H136" s="14">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I136" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: انواع گردوها</v>
+        <v>Done</v>
       </c>
       <c r="J136" s="39" t="s">
         <v>155</v>
@@ -15005,20 +15021,20 @@
         <v>25</v>
       </c>
       <c r="E137" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="20"/>
       <c r="G137" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H137" s="14">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I137" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: نوار کناری</v>
+        <v>Done</v>
       </c>
       <c r="J137" s="39" t="s">
         <v>155</v>
@@ -15041,20 +15057,20 @@
         <v>10</v>
       </c>
       <c r="E138" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="20"/>
       <c r="G138" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H138" s="14">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I138" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: مرز کاشت</v>
+        <v>Done</v>
       </c>
       <c r="J138" s="39" t="s">
         <v>155</v>
@@ -15077,20 +15093,20 @@
         <v>30</v>
       </c>
       <c r="E139" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="20"/>
       <c r="G139" s="23">
         <f t="shared" ref="G139:G202" si="6">IF(E139,D139,IF(F139="",0,MIN(MAX(F139,0),D139)))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H139" s="14">
         <f t="shared" ref="H139:H202" si="7">MAX(D139-G139,0)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I139" s="10" t="str">
         <f t="shared" ref="I139:I202" si="8">IF(D139=0,"No points attached",IF(G139=D139,"Done",IF(G139=0,"Do: "&amp;C139,"Finish: "&amp;C139&amp;" ("&amp;TEXT(H139,"0.##")&amp;" pts left)")))</f>
-        <v>Do: حرکت گردوها</v>
+        <v>Done</v>
       </c>
       <c r="J139" s="39" t="s">
         <v>155</v>
@@ -15113,20 +15129,20 @@
         <v>50</v>
       </c>
       <c r="E140" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="20"/>
       <c r="G140" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H140" s="14">
         <f t="shared" si="7"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I140" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: فهرست زامبی‌ها</v>
+        <v>Done</v>
       </c>
       <c r="J140" s="39" t="s">
         <v>155</v>
@@ -15149,20 +15165,20 @@
         <v>25</v>
       </c>
       <c r="E141" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="20"/>
       <c r="G141" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H141" s="14">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I141" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: انیمیشن کاشت</v>
+        <v>Done</v>
       </c>
       <c r="J141" s="39" t="s">
         <v>155</v>
@@ -15185,20 +15201,20 @@
         <v>25</v>
       </c>
       <c r="E142" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="20"/>
       <c r="G142" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H142" s="14">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I142" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: سطر کاشت</v>
+        <v>Done</v>
       </c>
       <c r="J142" s="39" t="s">
         <v>155</v>
@@ -15221,20 +15237,20 @@
         <v>30</v>
       </c>
       <c r="E143" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="20"/>
       <c r="G143" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H143" s="14">
         <f t="shared" si="7"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I143" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: تولید کنندگان</v>
+        <v>Done</v>
       </c>
       <c r="J143" s="39" t="s">
         <v>155</v>
@@ -15257,20 +15273,20 @@
         <v>20</v>
       </c>
       <c r="E144" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="20"/>
       <c r="G144" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H144" s="14">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I144" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: نمایش مغز‌ها</v>
+        <v>Done</v>
       </c>
       <c r="J144" s="39" t="s">
         <v>155</v>
@@ -23423,7 +23439,7 @@
       </c>
       <c r="BO5" s="28">
         <f>'Phase 2'!G76</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BP5" s="28">
         <f>'Phase 2'!G77</f>
@@ -23507,11 +23523,11 @@
       </c>
       <c r="CJ5" s="28">
         <f>'Phase 2'!G97</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="CK5" s="28">
         <f>'Phase 2'!G98</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="CL5" s="28">
         <f>'Phase 2'!G99</f>
@@ -23543,7 +23559,7 @@
       </c>
       <c r="CS5" s="28">
         <f>'Phase 2'!G106</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CT5" s="28">
         <f>'Phase 2'!G107</f>
@@ -23651,51 +23667,51 @@
       </c>
       <c r="DT5" s="28">
         <f>'Phase 2'!G133</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="DU5" s="28">
         <f>'Phase 2'!G134</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DV5" s="28">
         <f>'Phase 2'!G135</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="DW5" s="28">
         <f>'Phase 2'!G136</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DX5" s="28">
         <f>'Phase 2'!G137</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DY5" s="28">
         <f>'Phase 2'!G138</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="DZ5" s="28">
         <f>'Phase 2'!G139</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="EA5" s="28">
         <f>'Phase 2'!G140</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="EB5" s="28">
         <f>'Phase 2'!G141</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="EC5" s="28">
         <f>'Phase 2'!G142</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="ED5" s="28">
         <f>'Phase 2'!G143</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="EE5" s="28">
         <f>'Phase 2'!G144</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="EF5" s="28">
         <f>'Phase 2'!G145</f>
@@ -24103,7 +24119,7 @@
       <c r="IE5" s="28"/>
       <c r="IF5" s="28">
         <f>SUM(E5:EO5)</f>
-        <v>2960</v>
+        <v>3520</v>
       </c>
       <c r="IG5" s="28">
         <f>SUM(EP5:GN5)</f>
@@ -24111,7 +24127,7 @@
       </c>
       <c r="IH5" s="28">
         <f>MIN(IF5+IG5,IF4)</f>
-        <v>3325</v>
+        <v>3885</v>
       </c>
       <c r="II5" s="28">
         <f>MIN(SUM(GO5:IA5,MAX(IG5+IF5-IF4,0)/3),II4)</f>

--- a/ap project documents/AP_project_2026_one_team_tracker.xlsx
+++ b/ap project documents/AP_project_2026_one_team_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arian\Desktop\uni\AP\Project\Plants-vs-Zombies-2\ap project documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FA4A14-6656-4A42-BF40-3DF7B1EA6FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5747C909-1957-4C91-8EFE-EE2AE2065727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B11" s="36">
         <f>_logic_p2!IF5</f>
-        <v>3520</v>
+        <v>3740</v>
       </c>
       <c r="C11" s="30">
         <f>_logic_p2!IF4</f>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D11" s="33">
         <f t="shared" si="0"/>
-        <v>0.8702101359703337</v>
+        <v>0.92459826946847956</v>
       </c>
       <c r="F11" s="51"/>
       <c r="G11" s="52"/>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="B13" s="36">
         <f>_logic_p2!IH5</f>
-        <v>3885</v>
+        <v>4045</v>
       </c>
       <c r="C13" s="30">
         <f>_logic_p2!IH4</f>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="D13" s="33">
         <f t="shared" si="0"/>
-        <v>0.9604449938195303</v>
+        <v>1</v>
       </c>
       <c r="F13" s="51"/>
       <c r="G13" s="52"/>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="B14" s="37">
         <f>_logic_p2!II5</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C14" s="31">
         <f>_logic_p2!II4</f>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D14" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.3952095808383235E-2</v>
       </c>
       <c r="F14" s="54"/>
       <c r="G14" s="55"/>
@@ -10417,7 +10417,7 @@
     <row r="8" spans="1:11" ht="17.399999999999999">
       <c r="A8" s="61" t="str">
         <f>_logic_p2!IF5&amp;" / "&amp;_logic_p2!IF4</f>
-        <v>3520 / 4045</v>
+        <v>3740 / 4045</v>
       </c>
       <c r="B8" s="61"/>
       <c r="C8" s="61" t="str">
@@ -10427,12 +10427,12 @@
       <c r="D8" s="61"/>
       <c r="E8" s="61" t="str">
         <f>_logic_p2!IH5&amp;" / "&amp;_logic_p2!IH4</f>
-        <v>3885 / 4045</v>
+        <v>4045 / 4045</v>
       </c>
       <c r="F8" s="61"/>
       <c r="G8" s="61" t="str">
         <f>_logic_p2!II5&amp;" / "&amp;_logic_p2!II4</f>
-        <v>0 / 835</v>
+        <v>20 / 835</v>
       </c>
       <c r="H8" s="61"/>
     </row>
@@ -15309,20 +15309,20 @@
         <v>25</v>
       </c>
       <c r="E145" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="20"/>
       <c r="G145" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H145" s="14">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I145" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: نمایش گردباد</v>
+        <v>Done</v>
       </c>
       <c r="J145" s="39" t="s">
         <v>155</v>
@@ -15345,20 +15345,20 @@
         <v>25</v>
       </c>
       <c r="E146" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="20"/>
       <c r="G146" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H146" s="14">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I146" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: بادهای یخی</v>
+        <v>Done</v>
       </c>
       <c r="J146" s="39" t="s">
         <v>155</v>
@@ -15381,20 +15381,20 @@
         <v>10</v>
       </c>
       <c r="E147" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="20"/>
       <c r="G147" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H147" s="14">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I147" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: نمایش زمین‌های لیز</v>
+        <v>Done</v>
       </c>
       <c r="J147" s="39" t="s">
         <v>155</v>
@@ -15417,20 +15417,20 @@
         <v>25</v>
       </c>
       <c r="E148" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="20"/>
       <c r="G148" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H148" s="14">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I148" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: زامبی‌های یخ‌زده</v>
+        <v>Done</v>
       </c>
       <c r="J148" s="39" t="s">
         <v>155</v>
@@ -15453,20 +15453,20 @@
         <v>50</v>
       </c>
       <c r="E149" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" s="20"/>
       <c r="G149" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H149" s="14">
         <f t="shared" si="7"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I149" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: آب دریا</v>
+        <v>Done</v>
       </c>
       <c r="J149" s="39" t="s">
         <v>155</v>
@@ -15489,20 +15489,20 @@
         <v>20</v>
       </c>
       <c r="E150" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" s="20"/>
       <c r="G150" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H150" s="14">
         <f t="shared" si="7"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I150" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: تغییر سطح آب</v>
+        <v>Done</v>
       </c>
       <c r="J150" s="39" t="s">
         <v>155</v>
@@ -15525,20 +15525,20 @@
         <v>10</v>
       </c>
       <c r="E151" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="20"/>
       <c r="G151" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H151" s="14">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I151" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: مرز آب دریا</v>
+        <v>Done</v>
       </c>
       <c r="J151" s="39" t="s">
         <v>155</v>
@@ -15561,20 +15561,20 @@
         <v>15</v>
       </c>
       <c r="E152" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="20"/>
       <c r="G152" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H152" s="14">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I152" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: نمایش ساحل‌های پست</v>
+        <v>Done</v>
       </c>
       <c r="J152" s="39" t="s">
         <v>155</v>
@@ -15597,20 +15597,20 @@
         <v>25</v>
       </c>
       <c r="E153" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="20"/>
       <c r="G153" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H153" s="14">
         <f t="shared" si="7"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I153" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: انواع قبر</v>
+        <v>Done</v>
       </c>
       <c r="J153" s="39" t="s">
         <v>155</v>
@@ -15633,20 +15633,20 @@
         <v>15</v>
       </c>
       <c r="E154" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" s="20"/>
       <c r="G154" s="23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H154" s="14">
         <f t="shared" si="7"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I154" s="10" t="str">
         <f t="shared" si="8"/>
-        <v>Do: خانه‌های نکرومنسی</v>
+        <v>Done</v>
       </c>
       <c r="J154" s="39" t="s">
         <v>155</v>
@@ -23715,43 +23715,43 @@
       </c>
       <c r="EF5" s="28">
         <f>'Phase 2'!G145</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="EG5" s="28">
         <f>'Phase 2'!G146</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="EH5" s="28">
         <f>'Phase 2'!G147</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="EI5" s="28">
         <f>'Phase 2'!G148</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="EJ5" s="28">
         <f>'Phase 2'!G149</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="EK5" s="28">
         <f>'Phase 2'!G150</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="EL5" s="28">
         <f>'Phase 2'!G151</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="EM5" s="28">
         <f>'Phase 2'!G152</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="EN5" s="28">
         <f>'Phase 2'!G153</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="EO5" s="28">
         <f>'Phase 2'!G154</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="EP5" s="28">
         <f>'Phase 2'!G155</f>
@@ -24119,7 +24119,7 @@
       <c r="IE5" s="28"/>
       <c r="IF5" s="28">
         <f>SUM(E5:EO5)</f>
-        <v>3520</v>
+        <v>3740</v>
       </c>
       <c r="IG5" s="28">
         <f>SUM(EP5:GN5)</f>
@@ -24127,11 +24127,11 @@
       </c>
       <c r="IH5" s="28">
         <f>MIN(IF5+IG5,IF4)</f>
-        <v>3885</v>
+        <v>4045</v>
       </c>
       <c r="II5" s="28">
         <f>MIN(SUM(GO5:IA5,MAX(IG5+IF5-IF4,0)/3),II4)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/ap project documents/AP_project_2026_one_team_tracker.xlsx
+++ b/ap project documents/AP_project_2026_one_team_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arian\Desktop\uni\AP\Project\Plants-vs-Zombies-2\ap project documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5747C909-1957-4C91-8EFE-EE2AE2065727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8464E5-9CFE-42EE-8D32-2D1E2B7BFD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="B14" s="37">
         <f>_logic_p2!II5</f>
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="C14" s="31">
         <f>_logic_p2!II4</f>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D14" s="34">
         <f t="shared" si="0"/>
-        <v>2.3952095808383235E-2</v>
+        <v>0.12574850299401197</v>
       </c>
       <c r="F14" s="54"/>
       <c r="G14" s="55"/>
@@ -10432,7 +10432,7 @@
       <c r="F8" s="61"/>
       <c r="G8" s="61" t="str">
         <f>_logic_p2!II5&amp;" / "&amp;_logic_p2!II4</f>
-        <v>20 / 835</v>
+        <v>105 / 835</v>
       </c>
       <c r="H8" s="61"/>
     </row>
@@ -17505,20 +17505,20 @@
         <v>55</v>
       </c>
       <c r="E206" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F206" s="20"/>
       <c r="G206" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H206" s="14">
         <f t="shared" si="10"/>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="I206" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: گیاهان امتیازی</v>
+        <v>Done</v>
       </c>
       <c r="J206" s="39" t="s">
         <v>156</v>
@@ -17541,20 +17541,20 @@
         <v>30</v>
       </c>
       <c r="E207" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F207" s="20"/>
       <c r="G207" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H207" s="14">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I207" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: زامبی‌های امتیازی</v>
+        <v>Done</v>
       </c>
       <c r="J207" s="39" t="s">
         <v>156</v>
@@ -23959,11 +23959,11 @@
       </c>
       <c r="GO5" s="28">
         <f>'Phase 2'!G206</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="GP5" s="28">
         <f>'Phase 2'!G207</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="GQ5" s="28">
         <f>'Phase 2'!G208</f>
@@ -24131,7 +24131,7 @@
       </c>
       <c r="II5" s="28">
         <f>MIN(SUM(GO5:IA5,MAX(IG5+IF5-IF4,0)/3),II4)</f>
-        <v>20</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/ap project documents/AP_project_2026_one_team_tracker.xlsx
+++ b/ap project documents/AP_project_2026_one_team_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arian\Desktop\uni\AP\Project\Plants-vs-Zombies-2\ap project documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8464E5-9CFE-42EE-8D32-2D1E2B7BFD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331A82A6-F326-4FF2-8487-DCDCA4320BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="B14" s="37">
         <f>_logic_p2!II5</f>
-        <v>105</v>
+        <v>330</v>
       </c>
       <c r="C14" s="31">
         <f>_logic_p2!II4</f>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D14" s="34">
         <f t="shared" si="0"/>
-        <v>0.12574850299401197</v>
+        <v>0.39520958083832336</v>
       </c>
       <c r="F14" s="54"/>
       <c r="G14" s="55"/>
@@ -10432,7 +10432,7 @@
       <c r="F8" s="61"/>
       <c r="G8" s="61" t="str">
         <f>_logic_p2!II5&amp;" / "&amp;_logic_p2!II4</f>
-        <v>105 / 835</v>
+        <v>330 / 835</v>
       </c>
       <c r="H8" s="61"/>
     </row>
@@ -17793,20 +17793,20 @@
         <v>5</v>
       </c>
       <c r="E214" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F214" s="20"/>
       <c r="G214" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H214" s="14">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I214" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: نوار کناری در مراحل زامباس</v>
+        <v>Done</v>
       </c>
       <c r="J214" s="39" t="s">
         <v>156</v>
@@ -17829,20 +17829,20 @@
         <v>20</v>
       </c>
       <c r="E215" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215" s="20"/>
       <c r="G215" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H215" s="14">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I215" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: اشغال دو سطر</v>
+        <v>Done</v>
       </c>
       <c r="J215" s="39" t="s">
         <v>156</v>
@@ -17865,20 +17865,20 @@
         <v>15</v>
       </c>
       <c r="E216" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F216" s="20"/>
       <c r="G216" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H216" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I216" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: نوار جان</v>
+        <v>Done</v>
       </c>
       <c r="J216" s="39" t="s">
         <v>156</v>
@@ -17901,20 +17901,20 @@
         <v>25</v>
       </c>
       <c r="E217" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217" s="20"/>
       <c r="G217" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H217" s="14">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I217" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: گیج شدن</v>
+        <v>Done</v>
       </c>
       <c r="J217" s="39" t="s">
         <v>156</v>
@@ -17937,20 +17937,20 @@
         <v>30</v>
       </c>
       <c r="E218" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" s="20"/>
       <c r="G218" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H218" s="14">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I218" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: ظاهر کردن زامبی‌ها</v>
+        <v>Done</v>
       </c>
       <c r="J218" s="39" t="s">
         <v>156</v>
@@ -17973,20 +17973,20 @@
         <v>25</v>
       </c>
       <c r="E219" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F219" s="20"/>
       <c r="G219" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H219" s="14">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I219" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: جابه‌جایی بین سطر‌ها</v>
+        <v>Done</v>
       </c>
       <c r="J219" s="39" t="s">
         <v>156</v>
@@ -18261,20 +18261,20 @@
         <v>25</v>
       </c>
       <c r="E227" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F227" s="20"/>
       <c r="G227" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H227" s="14">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I227" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: موشک</v>
+        <v>Done</v>
       </c>
       <c r="J227" s="39" t="s">
         <v>156</v>
@@ -18297,20 +18297,20 @@
         <v>20</v>
       </c>
       <c r="E228" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F228" s="20"/>
       <c r="G228" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H228" s="14">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I228" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: حرکت سریع به جلو</v>
+        <v>Done</v>
       </c>
       <c r="J228" s="39" t="s">
         <v>156</v>
@@ -18333,20 +18333,20 @@
         <v>15</v>
       </c>
       <c r="E229" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F229" s="20"/>
       <c r="G229" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H229" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I229" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن موشک</v>
+        <v>Done</v>
       </c>
       <c r="J229" s="39" t="s">
         <v>156</v>
@@ -18369,20 +18369,20 @@
         <v>15</v>
       </c>
       <c r="E230" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F230" s="20"/>
       <c r="G230" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H230" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I230" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن ظاهر کردن زامبی</v>
+        <v>Done</v>
       </c>
       <c r="J230" s="39" t="s">
         <v>156</v>
@@ -18405,20 +18405,20 @@
         <v>15</v>
       </c>
       <c r="E231" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F231" s="20"/>
       <c r="G231" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H231" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I231" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن راه رفتن</v>
+        <v>Done</v>
       </c>
       <c r="J231" s="39" t="s">
         <v>156</v>
@@ -18441,20 +18441,20 @@
         <v>15</v>
       </c>
       <c r="E232" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F232" s="20"/>
       <c r="G232" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H232" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I232" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن حالت بیکار</v>
+        <v>Done</v>
       </c>
       <c r="J232" s="39" t="s">
         <v>156</v>
@@ -23991,27 +23991,27 @@
       </c>
       <c r="GW5" s="28">
         <f>'Phase 2'!G214</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="GX5" s="28">
         <f>'Phase 2'!G215</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="GY5" s="28">
         <f>'Phase 2'!G216</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="GZ5" s="28">
         <f>'Phase 2'!G217</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="HA5" s="28">
         <f>'Phase 2'!G218</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="HB5" s="28">
         <f>'Phase 2'!G219</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="HC5" s="28">
         <f>'Phase 2'!G220</f>
@@ -24043,27 +24043,27 @@
       </c>
       <c r="HJ5" s="28">
         <f>'Phase 2'!G227</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="HK5" s="28">
         <f>'Phase 2'!G228</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="HL5" s="28">
         <f>'Phase 2'!G229</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HM5" s="28">
         <f>'Phase 2'!G230</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HN5" s="28">
         <f>'Phase 2'!G231</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HO5" s="28">
         <f>'Phase 2'!G232</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HP5" s="28">
         <f>'Phase 2'!G233</f>
@@ -24131,7 +24131,7 @@
       </c>
       <c r="II5" s="28">
         <f>MIN(SUM(GO5:IA5,MAX(IG5+IF5-IF4,0)/3),II4)</f>
-        <v>105</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/ap project documents/AP_project_2026_one_team_tracker.xlsx
+++ b/ap project documents/AP_project_2026_one_team_tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arian\Desktop\uni\AP\Project\Plants-vs-Zombies-2\ap project documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HAMAHANG\code\Plants-vs-Zombies-2\ap project documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331A82A6-F326-4FF2-8487-DCDCA4320BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="7" r:id="rId1"/>
@@ -21,23 +21,7 @@
     <sheet name="_logic_p1" sheetId="2" state="hidden" r:id="rId6"/>
     <sheet name="_logic_p2" sheetId="3" state="hidden" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -2860,18 +2844,27 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2901,15 +2894,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3344,38 +3328,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.8" customHeight="1">
-      <c r="A1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="3" spans="1:8" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
     </row>
     <row r="5" spans="1:8" ht="27.15" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
@@ -3390,11 +3374,11 @@
       <c r="D7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
@@ -3412,11 +3396,11 @@
         <f t="shared" ref="D8:D14" si="0">IF(C8=0,0,B8/C8)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="49"/>
-      <c r="H8" s="50"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="5" t="s">
@@ -3434,9 +3418,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="51"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="53"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="58"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="5" t="s">
@@ -3454,9 +3438,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="51"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="53"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="58"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="5" t="s">
@@ -3474,9 +3458,9 @@
         <f t="shared" si="0"/>
         <v>0.92459826946847956</v>
       </c>
-      <c r="F11" s="51"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="53"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="58"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
@@ -3494,9 +3478,9 @@
         <f t="shared" si="0"/>
         <v>0.15051546391752577</v>
       </c>
-      <c r="F12" s="51"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="53"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="58"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="5" t="s">
@@ -3514,9 +3498,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="51"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="53"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="58"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="6" t="s">
@@ -3534,21 +3518,21 @@
         <f t="shared" si="0"/>
         <v>0.39520958083832336</v>
       </c>
-      <c r="F14" s="54"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="56"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="61"/>
     </row>
     <row r="16" spans="1:8" ht="14.4">
-      <c r="A16" s="41" t="s">
+      <c r="A16" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3619,58 +3603,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.65" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="57" t="str">
+      <c r="B3" s="45" t="str">
         <f>Dashboard!$B$3</f>
         <v>My Team</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="59"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
     </row>
     <row r="5" spans="1:11" ht="22.35" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="60"/>
+      <c r="B7" s="41"/>
     </row>
     <row r="8" spans="1:11" ht="17.399999999999999">
-      <c r="A8" s="61" t="str">
+      <c r="A8" s="42" t="str">
         <f>IF(_logic_p0!BA5="",0,_logic_p0!BA5)&amp;" / "&amp;_logic_p0!BA4</f>
         <v>0 / 380</v>
       </c>
-      <c r="B8" s="61"/>
+      <c r="B8" s="42"/>
     </row>
     <row r="10" spans="1:11" ht="24" customHeight="1">
       <c r="A10" s="2" t="s">
@@ -5596,67 +5580,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.65" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="57" t="str">
+      <c r="B3" s="45" t="str">
         <f>Dashboard!$B$3</f>
         <v>My Team</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="59"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
     </row>
     <row r="5" spans="1:11" ht="22.35" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="60" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60" t="s">
+      <c r="A7" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="60"/>
+      <c r="D7" s="41"/>
     </row>
     <row r="8" spans="1:11" ht="17.399999999999999">
-      <c r="A8" s="61" t="str">
+      <c r="A8" s="42" t="str">
         <f>_logic_p1!EE5&amp;" / "&amp;_logic_p1!EE4</f>
         <v>0 / 5495</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61" t="str">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42" t="str">
         <f>_logic_p1!EF5&amp;" / "&amp;_logic_p1!EF4</f>
         <v>0 / 60</v>
       </c>
-      <c r="D8" s="61"/>
+      <c r="D8" s="42"/>
     </row>
     <row r="10" spans="1:11" ht="24" customHeight="1">
       <c r="A10" s="2" t="s">
@@ -10356,85 +10340,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.65" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
         <v>393</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
     </row>
     <row r="3" spans="1:11" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="57" t="str">
+      <c r="B3" s="45" t="str">
         <f>Dashboard!$B$3</f>
         <v>My Team</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="59"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
     </row>
     <row r="5" spans="1:11" ht="22.35" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="60" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60" t="s">
+      <c r="A7" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41" t="s">
         <v>394</v>
       </c>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60" t="s">
+      <c r="D7" s="41"/>
+      <c r="E7" s="41" t="s">
         <v>395</v>
       </c>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60" t="s">
+      <c r="F7" s="41"/>
+      <c r="G7" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H7" s="60"/>
+      <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:11" ht="17.399999999999999">
-      <c r="A8" s="61" t="str">
+      <c r="A8" s="42" t="str">
         <f>_logic_p2!IF5&amp;" / "&amp;_logic_p2!IF4</f>
         <v>3740 / 4045</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61" t="str">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42" t="str">
         <f>_logic_p2!IG5&amp;" / "&amp;_logic_p2!IG4</f>
         <v>365 / 2425</v>
       </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61" t="str">
+      <c r="D8" s="42"/>
+      <c r="E8" s="42" t="str">
         <f>_logic_p2!IH5&amp;" / "&amp;_logic_p2!IH4</f>
         <v>4045 / 4045</v>
       </c>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61" t="str">
+      <c r="F8" s="42"/>
+      <c r="G8" s="42" t="str">
         <f>_logic_p2!II5&amp;" / "&amp;_logic_p2!II4</f>
         <v>330 / 835</v>
       </c>
-      <c r="H8" s="61"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="10" spans="1:11" ht="24" customHeight="1">
       <c r="A10" s="2" t="s">

--- a/ap project documents/AP_project_2026_one_team_tracker.xlsx
+++ b/ap project documents/AP_project_2026_one_team_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HAMAHANG\code\Plants-vs-Zombies-2\ap project documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331A82A6-F326-4FF2-8487-DCDCA4320BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A8DB7B-B9E5-40F7-9152-9589CEA8C0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B14" s="37">
         <f>_logic_p2!II5</f>
-        <v>330</v>
+        <v>535</v>
       </c>
       <c r="C14" s="31">
         <f>_logic_p2!II4</f>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="D14" s="34">
         <f t="shared" si="0"/>
-        <v>0.39520958083832336</v>
+        <v>0.64071856287425155</v>
       </c>
       <c r="F14" s="59"/>
       <c r="G14" s="60"/>
@@ -10416,7 +10416,7 @@
       <c r="F8" s="42"/>
       <c r="G8" s="42" t="str">
         <f>_logic_p2!II5&amp;" / "&amp;_logic_p2!II4</f>
-        <v>330 / 835</v>
+        <v>535 / 835</v>
       </c>
       <c r="H8" s="42"/>
     </row>
@@ -18461,20 +18461,20 @@
         <v>15</v>
       </c>
       <c r="E233" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F233" s="20"/>
       <c r="G233" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H233" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I233" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: موشک ماموت</v>
+        <v>Done</v>
       </c>
       <c r="J233" s="39" t="s">
         <v>156</v>
@@ -18497,20 +18497,20 @@
         <v>15</v>
       </c>
       <c r="E234" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F234" s="20"/>
       <c r="G234" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H234" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I234" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: باد یخی ماموت</v>
+        <v>Done</v>
       </c>
       <c r="J234" s="39" t="s">
         <v>156</v>
@@ -18533,20 +18533,20 @@
         <v>25</v>
       </c>
       <c r="E235" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F235" s="20"/>
       <c r="G235" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H235" s="14">
         <f t="shared" si="10"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I235" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: زامبی‌های یخ‌زده</v>
+        <v>Done</v>
       </c>
       <c r="J235" s="39" t="s">
         <v>156</v>
@@ -18569,20 +18569,20 @@
         <v>15</v>
       </c>
       <c r="E236" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F236" s="20"/>
       <c r="G236" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H236" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I236" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن باد یخی</v>
+        <v>Done</v>
       </c>
       <c r="J236" s="39" t="s">
         <v>156</v>
@@ -18605,20 +18605,20 @@
         <v>15</v>
       </c>
       <c r="E237" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F237" s="20"/>
       <c r="G237" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H237" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I237" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن حالت بیکار</v>
+        <v>Done</v>
       </c>
       <c r="J237" s="39" t="s">
         <v>156</v>
@@ -18641,20 +18641,20 @@
         <v>15</v>
       </c>
       <c r="E238" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F238" s="20"/>
       <c r="G238" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H238" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I238" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن پرتاب موشک</v>
+        <v>Done</v>
       </c>
       <c r="J238" s="39" t="s">
         <v>156</v>
@@ -18677,20 +18677,20 @@
         <v>15</v>
       </c>
       <c r="E239" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F239" s="20"/>
       <c r="G239" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H239" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I239" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن ظاهر کردن زامبی یخی</v>
+        <v>Done</v>
       </c>
       <c r="J239" s="39" t="s">
         <v>156</v>
@@ -18713,20 +18713,20 @@
         <v>15</v>
       </c>
       <c r="E240" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F240" s="20"/>
       <c r="G240" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H240" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I240" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: کوسه‌های کوچک</v>
+        <v>Done</v>
       </c>
       <c r="J240" s="39" t="s">
         <v>156</v>
@@ -18749,20 +18749,20 @@
         <v>30</v>
       </c>
       <c r="E241" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F241" s="20"/>
       <c r="G241" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H241" s="14">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I241" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: توربین</v>
+        <v>Done</v>
       </c>
       <c r="J241" s="39" t="s">
         <v>156</v>
@@ -18785,20 +18785,20 @@
         <v>15</v>
       </c>
       <c r="E242" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F242" s="20"/>
       <c r="G242" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H242" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I242" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن حالت بیکار</v>
+        <v>Done</v>
       </c>
       <c r="J242" s="39" t="s">
         <v>156</v>
@@ -18820,21 +18820,21 @@
       <c r="D243" s="15">
         <v>15</v>
       </c>
-      <c r="E243" s="18" t="b">
-        <v>0</v>
+      <c r="E243" s="17" t="b">
+        <v>1</v>
       </c>
       <c r="F243" s="21"/>
       <c r="G243" s="24">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H243" s="15">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I243" s="12" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن توربین</v>
+        <v>Done</v>
       </c>
       <c r="J243" s="40" t="s">
         <v>156</v>
@@ -18856,20 +18856,20 @@
       <c r="D244">
         <v>15</v>
       </c>
-      <c r="E244" s="3" t="b">
-        <v>0</v>
+      <c r="E244" s="17" t="b">
+        <v>1</v>
       </c>
       <c r="G244">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H244">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I244" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن ظاهر کردن کوسه</v>
+        <v>Done</v>
       </c>
       <c r="J244" s="11" t="s">
         <v>156</v>
@@ -24051,51 +24051,51 @@
       </c>
       <c r="HP5" s="28">
         <f>'Phase 2'!G233</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HQ5" s="28">
         <f>'Phase 2'!G234</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HR5" s="28">
         <f>'Phase 2'!G235</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="HS5" s="28">
         <f>'Phase 2'!G236</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HT5" s="28">
         <f>'Phase 2'!G237</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HU5" s="28">
         <f>'Phase 2'!G238</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HV5" s="28">
         <f>'Phase 2'!G239</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HW5" s="28">
         <f>'Phase 2'!G240</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HX5" s="28">
         <f>'Phase 2'!G241</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="HY5" s="28">
         <f>'Phase 2'!G242</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HZ5" s="28">
         <f>'Phase 2'!G243</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="IA5" s="28">
         <f>'Phase 2'!G244</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="IB5" s="28"/>
       <c r="IC5" s="28"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="II5" s="28">
         <f>MIN(SUM(GO5:IA5,MAX(IG5+IF5-IF4,0)/3),II4)</f>
-        <v>330</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>

--- a/ap project documents/AP_project_2026_one_team_tracker.xlsx
+++ b/ap project documents/AP_project_2026_one_team_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HAMAHANG\code\Plants-vs-Zombies-2\ap project documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A8DB7B-B9E5-40F7-9152-9589CEA8C0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269A4B5F-88E9-4274-8671-62175B608E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B11" s="36">
         <f>_logic_p2!IF5</f>
-        <v>3740</v>
+        <v>3800</v>
       </c>
       <c r="C11" s="30">
         <f>_logic_p2!IF4</f>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D11" s="33">
         <f t="shared" si="0"/>
-        <v>0.92459826946847956</v>
+        <v>0.93943139678615573</v>
       </c>
       <c r="F11" s="56"/>
       <c r="G11" s="57"/>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B12" s="36">
         <f>_logic_p2!IG5</f>
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="C12" s="30">
         <f>_logic_p2!IG4</f>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D12" s="33">
         <f t="shared" si="0"/>
-        <v>0.15051546391752577</v>
+        <v>0.16494845360824742</v>
       </c>
       <c r="F12" s="56"/>
       <c r="G12" s="57"/>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B14" s="37">
         <f>_logic_p2!II5</f>
-        <v>535</v>
+        <v>706.66666666666663</v>
       </c>
       <c r="C14" s="31">
         <f>_logic_p2!II4</f>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="D14" s="34">
         <f t="shared" si="0"/>
-        <v>0.64071856287425155</v>
+        <v>0.84630738522954085</v>
       </c>
       <c r="F14" s="59"/>
       <c r="G14" s="60"/>
@@ -10333,7 +10333,8 @@
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="8" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="36.19921875" customWidth="1"/>
     <col min="9" max="9" width="42" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
@@ -10401,12 +10402,12 @@
     <row r="8" spans="1:11" ht="17.399999999999999">
       <c r="A8" s="42" t="str">
         <f>_logic_p2!IF5&amp;" / "&amp;_logic_p2!IF4</f>
-        <v>3740 / 4045</v>
+        <v>3800 / 4045</v>
       </c>
       <c r="B8" s="42"/>
       <c r="C8" s="42" t="str">
         <f>_logic_p2!IG5&amp;" / "&amp;_logic_p2!IG4</f>
-        <v>365 / 2425</v>
+        <v>400 / 2425</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="42" t="str">
@@ -10416,7 +10417,7 @@
       <c r="F8" s="42"/>
       <c r="G8" s="42" t="str">
         <f>_logic_p2!II5&amp;" / "&amp;_logic_p2!II4</f>
-        <v>535 / 835</v>
+        <v>706.666666666667 / 835</v>
       </c>
       <c r="H8" s="42"/>
     </row>
@@ -13349,20 +13350,20 @@
         <v>60</v>
       </c>
       <c r="E91" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="20"/>
       <c r="G91" s="23">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H91" s="14">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I91" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>Do: سطوح یخ‌زدگی گیاهان</v>
+        <v>Done</v>
       </c>
       <c r="J91" s="39" t="s">
         <v>155</v>
@@ -17417,20 +17418,20 @@
         <v>35</v>
       </c>
       <c r="E204" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F204" s="20"/>
       <c r="G204" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H204" s="14">
         <f t="shared" si="10"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I204" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: نمایش تعداد غذای گیاه</v>
+        <v>Done</v>
       </c>
       <c r="J204" s="39" t="s">
         <v>394</v>
@@ -17993,20 +17994,20 @@
         <v>30</v>
       </c>
       <c r="E220" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" s="20"/>
       <c r="G220" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H220" s="14">
         <f t="shared" si="10"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I220" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: گلوله‌های آتشین</v>
+        <v>Done</v>
       </c>
       <c r="J220" s="39" t="s">
         <v>156</v>
@@ -18029,20 +18030,20 @@
         <v>40</v>
       </c>
       <c r="E221" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F221" s="20"/>
       <c r="G221" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H221" s="14">
         <f t="shared" si="10"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I221" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: آتش زدن دو ردیف</v>
+        <v>Done</v>
       </c>
       <c r="J221" s="39" t="s">
         <v>156</v>
@@ -18065,20 +18066,20 @@
         <v>10</v>
       </c>
       <c r="E222" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F222" s="20"/>
       <c r="G222" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H222" s="14">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I222" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: زمین‌های آتش گرفته</v>
+        <v>Done</v>
       </c>
       <c r="J222" s="39" t="s">
         <v>156</v>
@@ -18101,20 +18102,20 @@
         <v>15</v>
       </c>
       <c r="E223" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F223" s="20"/>
       <c r="G223" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H223" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I223" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن حالت بیکار</v>
+        <v>Done</v>
       </c>
       <c r="J223" s="39" t="s">
         <v>156</v>
@@ -18137,20 +18138,20 @@
         <v>15</v>
       </c>
       <c r="E224" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F224" s="20"/>
       <c r="G224" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H224" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I224" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن پرتاب گلوله</v>
+        <v>Done</v>
       </c>
       <c r="J224" s="39" t="s">
         <v>156</v>
@@ -18173,20 +18174,20 @@
         <v>15</v>
       </c>
       <c r="E225" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" s="20"/>
       <c r="G225" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H225" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I225" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن آتش زدن</v>
+        <v>Done</v>
       </c>
       <c r="J225" s="39" t="s">
         <v>156</v>
@@ -18209,20 +18210,20 @@
         <v>15</v>
       </c>
       <c r="E226" s="17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F226" s="20"/>
       <c r="G226" s="23">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H226" s="14">
         <f t="shared" si="10"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I226" s="10" t="str">
         <f t="shared" si="11"/>
-        <v>Do: انیمیشن گیج شدن</v>
+        <v>Done</v>
       </c>
       <c r="J226" s="39" t="s">
         <v>156</v>
@@ -23483,7 +23484,7 @@
       </c>
       <c r="CD5" s="28">
         <f>'Phase 2'!G91</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="CE5" s="28">
         <f>'Phase 2'!G92</f>
@@ -23935,7 +23936,7 @@
       </c>
       <c r="GM5" s="28">
         <f>'Phase 2'!G204</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="GN5" s="28">
         <f>'Phase 2'!G205</f>
@@ -23999,31 +24000,31 @@
       </c>
       <c r="HC5" s="28">
         <f>'Phase 2'!G220</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="HD5" s="28">
         <f>'Phase 2'!G221</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="HE5" s="28">
         <f>'Phase 2'!G222</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="HF5" s="28">
         <f>'Phase 2'!G223</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HG5" s="28">
         <f>'Phase 2'!G224</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HH5" s="28">
         <f>'Phase 2'!G225</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HI5" s="28">
         <f>'Phase 2'!G226</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="HJ5" s="28">
         <f>'Phase 2'!G227</f>
@@ -24103,11 +24104,11 @@
       <c r="IE5" s="28"/>
       <c r="IF5" s="28">
         <f>SUM(E5:EO5)</f>
-        <v>3740</v>
+        <v>3800</v>
       </c>
       <c r="IG5" s="28">
         <f>SUM(EP5:GN5)</f>
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="IH5" s="28">
         <f>MIN(IF5+IG5,IF4)</f>
@@ -24115,7 +24116,7 @@
       </c>
       <c r="II5" s="28">
         <f>MIN(SUM(GO5:IA5,MAX(IG5+IF5-IF4,0)/3),II4)</f>
-        <v>535</v>
+        <v>706.66666666666663</v>
       </c>
     </row>
   </sheetData>
